--- a/artfynd/A 55104-2025 artfynd.xlsx
+++ b/artfynd/A 55104-2025 artfynd.xlsx
@@ -1651,7 +1651,7 @@
         <v>133866870</v>
       </c>
       <c r="B10" t="n">
-        <v>99122</v>
+        <v>99129</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>133866892</v>
       </c>
       <c r="B11" t="n">
-        <v>99122</v>
+        <v>99129</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 55104-2025 artfynd.xlsx
+++ b/artfynd/A 55104-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>13516600</v>
+        <v>2040752</v>
       </c>
       <c r="B2" t="n">
-        <v>9302</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79707</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>101246</v>
+        <v>6431</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ekoxe</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lucanus cervus</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lilla Rimmö ekhage, Ög</t>
+          <t>LÖVSTAD EKHAGMARK, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>604084.456201831</v>
+        <v>604093</v>
       </c>
       <c r="R2" t="n">
-        <v>6478547.210215252</v>
+        <v>6478509</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,27 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2002-06-18</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1998-08-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2002-06-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1998-08-20</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>funnen död på marken, troligen nydöd</t>
+          <t>Ädellövskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,11 +761,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>ekhage</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -797,37 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2040752</v>
+        <v>1945063</v>
       </c>
       <c r="B3" t="n">
-        <v>77881</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6431</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -837,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>604092.8114151353</v>
+        <v>604093</v>
       </c>
       <c r="R3" t="n">
-        <v>6478509.193065557</v>
+        <v>6478509</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -870,19 +845,9 @@
           <t>1998-08-20</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1998-08-20</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -914,37 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1945063</v>
+        <v>1915248</v>
       </c>
       <c r="B4" t="n">
-        <v>78568</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -954,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>604092.8114151353</v>
+        <v>604093</v>
       </c>
       <c r="R4" t="n">
-        <v>6478509.193065557</v>
+        <v>6478509</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -987,19 +947,9 @@
           <t>1998-08-20</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1998-08-20</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1031,15 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1915248</v>
+        <v>13516600</v>
       </c>
       <c r="B5" t="n">
-        <v>78601</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>9406</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1047,37 +992,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6463</v>
+        <v>101246</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lucanus cervus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>LÖVSTAD EKHAGMARK, Ög</t>
+          <t>Lilla Rimmö ekhage, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>604092.8114151353</v>
+        <v>604084</v>
       </c>
       <c r="R5" t="n">
-        <v>6478509.193065557</v>
+        <v>6478547</v>
       </c>
       <c r="S5" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1101,27 +1046,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>1998-08-20</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2002-06-18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1998-08-20</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2002-06-18</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ädellövskog</t>
+          <t>funnen död på marken, troligen nydöd</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,6 +1067,11 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>ekhage</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1148,57 +1088,67 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>83155820</v>
+        <v>133866870</v>
       </c>
       <c r="B6" t="n">
-        <v>103812</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99136</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220785</v>
+        <v>219792</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Adam och eva</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dactylorhiza sambucina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>L:a Rimmö, Ög</t>
+          <t>Lilla Rimmöns ekhagar, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>603915.8464497029</v>
+        <v>603961</v>
       </c>
       <c r="R6" t="n">
-        <v>6478513.408716304</v>
+        <v>6478487</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1220,29 +1170,24 @@
           <t>Rönö</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>CA768B78-1629-4A57-9A10-CBA1963C0E11</t>
-        </is>
-      </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2005-11-18</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2005-11-18</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1257,73 +1202,79 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kenneth Claesson</t>
+          <t>William Rosén</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kenneth Claesson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Trädportalen</t>
-        </is>
-      </c>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>83155844</v>
+        <v>133866892</v>
       </c>
       <c r="B7" t="n">
-        <v>103812</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99136</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220785</v>
+        <v>219792</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Adam och eva</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dactylorhiza sambucina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>L:a Rimmö, Ög</t>
+          <t>Lilla Rimmöns ekhagar, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>604031.0186365333</v>
+        <v>604181</v>
       </c>
       <c r="R7" t="n">
-        <v>6478563.603145224</v>
+        <v>6478437</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1345,29 +1296,24 @@
           <t>Rönö</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>B9B3C367-CFA1-40D9-ACB7-72F5D2109338</t>
-        </is>
-      </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2005-11-18</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2005-11-18</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1382,31 +1328,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kenneth Claesson</t>
+          <t>William Rosén</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kenneth Claesson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Trädportalen</t>
-        </is>
-      </c>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>83155821</v>
+        <v>83155820</v>
       </c>
       <c r="B8" t="n">
-        <v>103812</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,10 +1379,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>603877.9497777735</v>
+        <v>603916</v>
       </c>
       <c r="R8" t="n">
-        <v>6478517.6437344</v>
+        <v>6478513</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1472,7 +1409,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>345EDAF5-19E0-4843-A129-F0C3DF9907DB</t>
+          <t>CA768B78-1629-4A57-9A10-CBA1963C0E11</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1480,19 +1417,9 @@
           <t>2005-11-18</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2005-11-18</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1523,15 +1450,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>83155835</v>
+        <v>83155821</v>
       </c>
       <c r="B9" t="n">
-        <v>103812</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1567,10 +1489,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>604144.6706021932</v>
+        <v>603878</v>
       </c>
       <c r="R9" t="n">
-        <v>6478690.759082058</v>
+        <v>6478518</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1597,7 +1519,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>61E688C4-2320-4A78-99BD-43B9F07323B8</t>
+          <t>345EDAF5-19E0-4843-A129-F0C3DF9907DB</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1605,19 +1527,9 @@
           <t>2005-11-18</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2005-11-18</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1648,67 +1560,52 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133866870</v>
+        <v>83155835</v>
       </c>
       <c r="B10" t="n">
-        <v>99129</v>
+        <v>106813</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219792</v>
+        <v>220785</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Adam och eva</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dactylorhiza sambucina</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lilla Rimmöns ekhagar, Ög</t>
+          <t>L:a Rimmö, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>603961</v>
+        <v>604145</v>
       </c>
       <c r="R10" t="n">
-        <v>6478487</v>
+        <v>6478691</v>
       </c>
       <c r="S10" t="n">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1730,24 +1627,19 @@
           <t>Rönö</t>
         </is>
       </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>61E688C4-2320-4A78-99BD-43B9F07323B8</t>
+        </is>
+      </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>10:16</t>
+          <t>2005-11-18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>10:16</t>
+          <t>2005-11-18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1762,79 +1654,68 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>William Rosén</t>
+          <t>Kenneth Claesson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>William Rosén</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Kenneth Claesson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133866892</v>
+        <v>83155844</v>
       </c>
       <c r="B11" t="n">
-        <v>99129</v>
+        <v>106813</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219792</v>
+        <v>220785</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Adam och eva</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza sambucina</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lilla Rimmöns ekhagar, Ög</t>
+          <t>L:a Rimmö, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>604181</v>
+        <v>604031</v>
       </c>
       <c r="R11" t="n">
-        <v>6478437</v>
+        <v>6478564</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1856,24 +1737,19 @@
           <t>Rönö</t>
         </is>
       </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>B9B3C367-CFA1-40D9-ACB7-72F5D2109338</t>
+        </is>
+      </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>09:43</t>
+          <t>2005-11-18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>09:43</t>
+          <t>2005-11-18</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1888,15 +1764,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>William Rosén</t>
+          <t>Kenneth Claesson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>William Rosén</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Kenneth Claesson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 55104-2025 artfynd.xlsx
+++ b/artfynd/A 55104-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2040752</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1945063</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1915248</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1085,6 +1105,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13516600</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1211,6 +1236,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133866870</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1337,6 +1367,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133866892</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1447,6 +1482,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83155820</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1557,6 +1597,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83155821</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1667,6 +1712,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83155835</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1777,8 +1827,25 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83155844</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>